--- a/medford_endoskopicheskie_stoyki.xlsx
+++ b/medford_endoskopicheskie_stoyki.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Что такое эндоскопическая стойка?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>endoskopicheskie_stoyki</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Сколько стоит эндоскопическая стойка?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>endoskopicheskie_stoyki</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>

--- a/medford_endoskopicheskie_stoyki.xlsx
+++ b/medford_endoskopicheskie_stoyki.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопические стойки для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker — всего 20 позиций.</t>
+          <t>Эндоскопические стойки для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_endoskopicheskie_stoyki.xlsx
+++ b/medford_endoskopicheskie_stoyki.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать эндоскопические стойки для клиники?</t>
+          <t>Что такое эндоскопическая стойка?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Область применения, Разрешение, пикселей, Страна производства, Производитель). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Это многофункциональная конструкция в виде тележки с секциями, служащая платформой для оборудования эндоскопических исследований и малоинвазивных операций. На ней размещают видеопроцессор, источник света, монитор, инсуффлятор и другие приборы. Стойка организует рабочее пространство, защищает технику от вибраций и повышает эргономику работы хирурга.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Что входит в комплектацию стойки?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Базовый комплекс включает основание с колёсами, стойку-колонну с креплениями, видеопроцессор, источник света, монитор, интерфейс управления и кабельные органайзеры, а для полостных операций — инсуффлятор и резервуар для промывки. Дополнительно ставят ЭХВЧ, аспирационно-ирригационный блок, шейверные системы и эндоскопические помпы.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какие бывают виды эндоскопических стоек?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>По мобильности — стационарные и мобильные (на колёсах с фиксаторами). По специализации — диагностические, операционные, универсальные и специализированные под конкретное направление. По классу — базовые, среднего и экспертного класса. По уровню автоматизации — механические и с сенсорными панелями и интеграцией с другими системами.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Чем отличается стойка 4K от Full HD?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Разрешение задаёт детализацию изображения. Full HD (1920×1080) достаточно для большинства стандартных вмешательств. Системы 4K Ultra HD (3840×2160 или 4096×2160), например Mindray HyPixel U1, Olympus Visera 4K UHD и Stryker 1688 AIM 4K, дают вчетверо больше пикселей и более чёткую картинку для сложных операций.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Какую стойку выбрать под лапароскопию?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Для лапароскопии нужен комплекс с видеосистемой, монитором, источником света и инсуффлятором для подачи газа в брюшную полость, при необходимости — ЭХВЧ и аспирационно-ирригационный блок. В каталоге под эти задачи подходят системы Эндомедиум, MGB, Olympus Visera и Mindray. Конкретную конфигурацию собирают под методики клиники.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопическая стойка?</t>
+          <t>Из чего сделан каркас стойки?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Каркас обычно изготавливают из прочных алюминиевых сплавов — они дают жёсткость и устойчивость при небольшом весе. Для усиленных элементов применяют нержавеющую сталь. Рабочие поверхности покрывают составами, устойчивыми к дезинфицирующим растворам, а на углах полок ставят противоударные бамперы.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит эндоскопическая стойка?</t>
+          <t>Можно ли собрать стойку из компонентов разных брендов?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Только при подтверждённой совместимости. Видеопроцессор, камера, источник света и эндоскопы рассчитаны на работу в единой платформе с общими разъёмами и протоколами. Смешивание компонентов разных производителей без официальной совместимости ведёт к потере функций. Состав согласуют с поставщиком под конкретные задачи.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопические стойки для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker.</t>
+          <t>Эндоскопические стойки — мобильные платформы, объединяющие оборудование для жёсткой эндоскопии и малоинвазивных операций: видеосистему, источник света, монитор, инсуффлятор и аспирационно-ирригационный блок. В категории представлены комплексы Mindray HyPixel U1 (4K Ultra HD, 3840×2160), Olympus Visera Elite II и Visera 4K UHD (4096×2160), стойки KARL STORZ, Stryker 1688 AIM 4K, Richard Wolf, MGB и решения Эндомедиум под лапароскопию, артроскопию, урологию, гинекологию и ЛОР. Стойка организует рабочее пространство, защищает приборы от вибраций и обеспечивает эргономику при длительных процедурах.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Классификация эндоскопических стоек</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопические стойки</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4440,243 +4440,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Классификация эндоскопических стоек</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Варианты</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Область применения</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Разрешение, пикселей</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
+          <t>Когда выбирают</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mindray HyPixel U1 эндоскопическая видеосистема 4K ULTRA HD</t>
+          <t>По мобильности</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>Стационарные / мобильные</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Общая хирургия</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>3840×2160</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Мобильные — для перемещения между залами</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Система эндоскопической визуализации для артроскопии Эндомедиум</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>По специализации</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Диагностические, операционные, универсальные, специализированные</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Артроскопия</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Под направление и объём работы</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Видеоэндоскопическая система Olympus Visera Elite II</t>
+          <t>По классу</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>Базовые, среднего, экспертного класса</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Гинекология</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>По сложности процедур</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Система эндоскопической визуализации для лапароскопии Эндомедиум</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>По автоматизации</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Механические / с сенсорными панелями</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Гинекология</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Экспертным операционным — интеграция</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Видеодерматоскоп Sometech Dr. Camscope DCS-105</t>
+          <t>По разрешению</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Sometech</t>
+          <t>Full HD / 4K Ultra HD</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Дерматология</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Видеоэндоскопическая система Olympus Visera 4K UHD</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Olympus</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Гинекология</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>4096×2160</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>4K — для сложных вмешательств</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4688,7 +4571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5014,12 +4897,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите направление хирургии</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается эндоскопические стойки: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Лапароскопия, артроскопия, урология, гинекология и ЛОР предъявляют разные требования к стойке. От специализации зависит набор блоков: инсуффлятор для лапароскопии, помпа и шейвер для артроскопии, комплекс ТУР для урологии. С этого начинается подбор.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5059,12 +4942,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите разрешение видеосистемы</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Разрешение определяет детализацию картинки. Full HD (1920×1080) закрывает большинство стандартных задач, 4K Ultra HD (3840×2160 у Mindray HyPixel U1, 4096×2160 у Olympus Visera 4K UHD и Stryker 1688 AIM 4K) даёт более детальное изображение для сложных вмешательств.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5104,12 +4987,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Определите базовую комплектацию</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Область применения, Разрешение, пикселей, Страна производства, Производитель. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Базовый комплекс включает основание с колёсами, стойку-колонну, видеопроцессор, источник света, монитор, а для полостных операций — инсуффлятор, резервуар для промывки и кабельные органайзеры. Сверьте состав с методиками кабинета, чтобы не переплачивать за лишние блоки.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5149,12 +5032,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Добавьте специализированные блоки</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker.</t>
+          <t>Под профиль клиники комплекс дополняют инсуффлятором, электрохирургическим аппаратом (ЭХВЧ), аспирационно-ирригационным блоком, шейверными системами и эндоскопическими помпами. Артроскопии нужна помпа и шейвер, урологии — ТУР-блок. Заложите нужные модули заранее.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5194,12 +5077,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените мобильность и эргономику</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Мобильная стойка на поворотных колёсах с фиксаторами перемещается между залами, стационарная жёстко закреплена. Регулировка высоты и угла наклона снижает утомляемость хирурга при длительных процедурах, а противоударные бамперы защищают приборы. Выберите исполнение под планировку операционной.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5239,12 +5122,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте совместимость компонентов</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Видеопроцессор, камера, источник света и эндоскопы должны образовывать одну совместимую платформу. Смешивание компонентов разных производителей без подтверждённой совместимости приводит к потере функций. Уточните у поставщика, какие эндоскопы и оптика подходят к выбранной стойке.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5294,7 +5177,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопические стойки подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker. При выборе обращают внимание на область применения, разрешение, страна производства, производитель, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Стойку подбирают под направление хирургии и класс операционной. Для лапароскопии и гинекологии критичны видеосистема, инсуффлятор и монитор, для артроскопии — помпа и шейвер, для урологии — комплекс с ТУР и цистоскопией. Разрешение задаёт видимость деталей: 4K-системы Olympus Visera 4K UHD, Stryker 1688 AIM 4K и Mindray HyPixel U1 дают более детальную картинку, чем Full HD. Собирайте комплектацию под реальные методики и следите за совместимостью эндоскопов и камеры.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5578,13 +5461,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопические стойки</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопические стойки — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Mindray, Olympus, Sometech, Richard Wolf, MGB, KARL STORZ, Stryker. Подберём вариант под задачи вашего отделения.</t>
+          <t>Эндоскопическая стойка — мобильная тележка с секциями, на которой размещают видеопроцессор, источник света, монитор, инсуффлятор, аспирационно-ирригационный блок и другие приборы для эндоскопических исследований и малоинвазивных операций. Стойки различают по мобильности, специализации (лапароскопия, артроскопия, урология, гинекология, ЛОР), классу и уровню автоматизации. В каталоге — комплексы Mindray, Olympus, KARL STORZ, Stryker, Richard Wolf, MGB и Эндомедиум с разрешением от Full HD до 4K Ultra HD (до 4096×2160). Комплектацию собирают под направление хирургии и класс операционной.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5621,13 +5504,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое эндоскопическая стойка</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Область применения, Разрешение, пикселей, Страна производства, Производитель), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Эндоскопическая стойка — специализированная тележка с несколькими секциями, которая служит платформой для комплекса оборудования при эндоскопических исследованиях и малоинвазивных операциях. Она компактно размещает приборы по вертикали, освобождает место в операционной, защищает чувствительную технику от вибраций и повреждений и повышает эргономику работы бригады.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5664,13 +5547,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Конструкция и материалы</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Каркас стойки изготавливают из прочных алюминиевых сплавов, для усиленных элементов применяют нержавеющую сталь, а поверхности покрывают составами, стойкими к дезинфектантам. В конструкции предусмотрены полки и держатели для эндоскопов, мониторов и ёмкостей, штативы для инфузий, кабельные органайзеры, поворотные колёса с фиксаторами и противоударные бамперы.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5707,13 +5590,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды и классификация стоек</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Стойки классифицируют по мобильности (стационарные и мобильные), специализации (диагностические, операционные, универсальные, специализированные), классу (базовые, среднего и экспертного класса) и уровню автоматизации (механические и с сенсорными панелями). Такая градация помогает подобрать решение под размер кабинета и сложность выполняемых процедур.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5730,6 +5613,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как выбрать эндоскопическую стойку</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Отталкивайтесь от направления хирургии и класса операционной: определите набор блоков (видеосистема, источник света, инсуффлятор, ЭХВЧ, помпа, шейвер), нужное разрешение (Full HD или 4K) и мобильность. Проверьте совместимость видеопроцессора, камеры и эндоскопов. В каталоге — комплексы Mindray, Olympus, KARL STORZ, Stryker, Richard Wolf, MGB и Эндомедиум.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>endoskopicheskie_stoyki</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
